--- a/QA_TestCase_BugReport.xlsx
+++ b/QA_TestCase_BugReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D146E85-4075-4EA9-B483-EFD5E9F9922D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241B70B8-4075-4F98-B19C-FA15700C8510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3645" yWindow="390" windowWidth="24030" windowHeight="14445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scope" sheetId="9" r:id="rId1"/>
@@ -455,10 +455,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>뷰포트와 동일하게 게임 내에서도 world 씬 내에서 ocean 노드 설정대로 포말과 파도가 지표면과 수평한 방향 (x축과 수평한 방향)과 수정된 값 (1.0) 높이로 발생</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>1. 게임 실행
 2. 파도 포말 방향, 파도 높이 확인</t>
     <phoneticPr fontId="9" type="noConversion"/>
@@ -1313,14 +1309,6 @@
   </si>
   <si>
     <t>Option 세부 항목</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>Spring0001 / 0.4.09</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>프로젝트명 / 테스트 빌드</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
@@ -1591,6 +1579,18 @@
     <t>1. 게임 실행
 2. Mainroom 내부 진입
 3. 내부 확인</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로젝트명</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spring0001</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>뷰포트와 동일하게 게임 내에서도 world 씬 내에서 ocean 노드 설정대로 포말 방향과 파도가 지표면과 수평한 방향 (x축과 수평한 방향)과 수정된 값 (1.0)의 높이로 발생</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -2560,7 +2560,131 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="54" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="52" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2576,7 +2700,10 @@
     <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2601,17 +2728,21 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2621,137 +2752,6 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="54" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="57" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="54" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3565,511 +3565,523 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="125" t="s">
+      <c r="A1" s="145" t="s">
+        <v>242</v>
+      </c>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+    </row>
+    <row r="2" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A2" s="128" t="s">
+        <v>241</v>
+      </c>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+    </row>
+    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="123" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="128" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+    </row>
+    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A4" s="121" t="s">
+        <v>292</v>
+      </c>
+      <c r="B4" s="142" t="s">
+        <v>293</v>
+      </c>
+      <c r="C4" s="130"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="130"/>
+      <c r="G4" s="90"/>
+    </row>
+    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A5" s="121" t="s">
+        <v>257</v>
+      </c>
+      <c r="B5" s="134" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="126"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-    </row>
-    <row r="2" spans="1:7" ht="21.95" customHeight="1">
-      <c r="A2" s="161" t="s">
-        <v>242</v>
-      </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="153"/>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153"/>
-    </row>
-    <row r="3" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="162" t="s">
-        <v>241</v>
-      </c>
-      <c r="B3" s="161" t="s">
-        <v>240</v>
-      </c>
-      <c r="C3" s="126"/>
-      <c r="D3" s="126"/>
-      <c r="E3" s="126"/>
-    </row>
-    <row r="4" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="149" t="s">
-        <v>269</v>
-      </c>
-      <c r="B4" s="127" t="s">
+      <c r="C5" s="130"/>
+      <c r="D5" s="130"/>
+      <c r="E5" s="130"/>
+    </row>
+    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A6" s="121" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="142" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="130"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="130"/>
+    </row>
+    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A7" s="121" t="s">
+        <v>237</v>
+      </c>
+      <c r="B7" s="134" t="s">
+        <v>278</v>
+      </c>
+      <c r="C7" s="130"/>
+      <c r="D7" s="130"/>
+      <c r="E7" s="130"/>
+    </row>
+    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="121" t="s">
+        <v>236</v>
+      </c>
+      <c r="B8" s="142" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="126"/>
-      <c r="D4" s="126"/>
-      <c r="E4" s="126"/>
-      <c r="G4" s="90"/>
-    </row>
-    <row r="5" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="149" t="s">
+      <c r="C8" s="130"/>
+      <c r="D8" s="130"/>
+      <c r="E8" s="130"/>
+    </row>
+    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="121" t="s">
+        <v>235</v>
+      </c>
+      <c r="B9" s="134" t="s">
         <v>258</v>
       </c>
-      <c r="B5" s="128" t="s">
+      <c r="C9" s="130"/>
+      <c r="D9" s="130"/>
+      <c r="E9" s="130"/>
+    </row>
+    <row r="10" spans="1:7" ht="21.95" customHeight="1">
+      <c r="A10" s="128" t="s">
+        <v>265</v>
+      </c>
+      <c r="B10" s="129"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="129"/>
+      <c r="E10" s="129"/>
+    </row>
+    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="123" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="123" t="s">
+        <v>234</v>
+      </c>
+      <c r="C11" s="123" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11" s="123" t="s">
+        <v>232</v>
+      </c>
+      <c r="E11" s="123" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="33.75" customHeight="1">
+      <c r="A12" s="109" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="103" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-    </row>
-    <row r="6" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="149" t="s">
-        <v>270</v>
-      </c>
-      <c r="B6" s="127" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="126"/>
-      <c r="D6" s="126"/>
-      <c r="E6" s="126"/>
-    </row>
-    <row r="7" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="149" t="s">
-        <v>238</v>
-      </c>
-      <c r="B7" s="128" t="s">
-        <v>281</v>
-      </c>
-      <c r="C7" s="126"/>
-      <c r="D7" s="126"/>
-      <c r="E7" s="126"/>
-    </row>
-    <row r="8" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="149" t="s">
-        <v>237</v>
-      </c>
-      <c r="B8" s="127" t="s">
-        <v>271</v>
-      </c>
-      <c r="C8" s="126"/>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126"/>
-    </row>
-    <row r="9" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="149" t="s">
-        <v>236</v>
-      </c>
-      <c r="B9" s="128" t="s">
+      <c r="C12" s="104" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" s="109">
+        <v>3</v>
+      </c>
+      <c r="E12" s="104" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="33.75" customHeight="1">
+      <c r="A13" s="110"/>
+      <c r="B13" s="105" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="106" t="s">
+        <v>229</v>
+      </c>
+      <c r="D13" s="110">
+        <v>1</v>
+      </c>
+      <c r="E13" s="106" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="33.75" customHeight="1">
+      <c r="A14" s="109"/>
+      <c r="B14" s="103" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="104" t="s">
         <v>259</v>
       </c>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-    </row>
-    <row r="10" spans="1:7" ht="21.95" customHeight="1">
-      <c r="A10" s="161" t="s">
-        <v>266</v>
-      </c>
-      <c r="B10" s="153"/>
-      <c r="C10" s="153"/>
-      <c r="D10" s="153"/>
-      <c r="E10" s="153"/>
-    </row>
-    <row r="11" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="162" t="s">
-        <v>68</v>
-      </c>
-      <c r="B11" s="162" t="s">
-        <v>235</v>
-      </c>
-      <c r="C11" s="162" t="s">
-        <v>234</v>
-      </c>
-      <c r="D11" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="E11" s="162" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="33.75" customHeight="1">
-      <c r="A12" s="135" t="s">
-        <v>116</v>
-      </c>
-      <c r="B12" s="129" t="s">
+      <c r="D14" s="109">
+        <v>4</v>
+      </c>
+      <c r="E14" s="104" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="33.75" customHeight="1">
+      <c r="A15" s="110" t="s">
+        <v>228</v>
+      </c>
+      <c r="B15" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="106" t="s">
+        <v>227</v>
+      </c>
+      <c r="D15" s="110">
+        <v>2</v>
+      </c>
+      <c r="E15" s="106" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="33.75" customHeight="1">
+      <c r="A16" s="109"/>
+      <c r="B16" s="103" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="104" t="s">
+        <v>263</v>
+      </c>
+      <c r="D16" s="109">
+        <v>4</v>
+      </c>
+      <c r="E16" s="104" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="33.75" customHeight="1">
+      <c r="A17" s="110" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="106" t="s">
+        <v>260</v>
+      </c>
+      <c r="D17" s="110">
+        <v>9</v>
+      </c>
+      <c r="E17" s="106" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="33.75" customHeight="1">
+      <c r="A18" s="109"/>
+      <c r="B18" s="103" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="104" t="s">
+        <v>261</v>
+      </c>
+      <c r="D18" s="109">
+        <v>2</v>
+      </c>
+      <c r="E18" s="104" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="33.75" customHeight="1">
+      <c r="A19" s="110" t="s">
         <v>245</v>
       </c>
-      <c r="C12" s="130" t="s">
-        <v>232</v>
-      </c>
-      <c r="D12" s="135">
+      <c r="B19" s="105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="106" t="s">
+        <v>246</v>
+      </c>
+      <c r="D19" s="110">
         <v>3</v>
       </c>
-      <c r="E12" s="130" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="33.75" customHeight="1">
-      <c r="A13" s="136"/>
-      <c r="B13" s="131" t="s">
-        <v>231</v>
-      </c>
-      <c r="C13" s="132" t="s">
-        <v>230</v>
-      </c>
-      <c r="D13" s="136">
-        <v>1</v>
-      </c>
-      <c r="E13" s="132" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="33.75" customHeight="1">
-      <c r="A14" s="135"/>
-      <c r="B14" s="129" t="s">
+      <c r="E19" s="106" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="33.75" customHeight="1">
+      <c r="A20" s="109"/>
+      <c r="B20" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="130" t="s">
-        <v>260</v>
-      </c>
-      <c r="D14" s="135">
+      <c r="C20" s="104" t="s">
+        <v>262</v>
+      </c>
+      <c r="D20" s="109">
         <v>4</v>
       </c>
-      <c r="E14" s="130" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="33.75" customHeight="1">
-      <c r="A15" s="136" t="s">
-        <v>229</v>
-      </c>
-      <c r="B15" s="131" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="132" t="s">
-        <v>228</v>
-      </c>
-      <c r="D15" s="136">
-        <v>2</v>
-      </c>
-      <c r="E15" s="132" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="33.75" customHeight="1">
-      <c r="A16" s="135"/>
-      <c r="B16" s="129" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="130" t="s">
-        <v>264</v>
-      </c>
-      <c r="D16" s="135">
-        <v>4</v>
-      </c>
-      <c r="E16" s="130" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="33.75" customHeight="1">
-      <c r="A17" s="136" t="s">
-        <v>112</v>
-      </c>
-      <c r="B17" s="131" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="132" t="s">
-        <v>261</v>
-      </c>
-      <c r="D17" s="136">
-        <v>9</v>
-      </c>
-      <c r="E17" s="132" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="33.75" customHeight="1">
-      <c r="A18" s="135"/>
-      <c r="B18" s="129" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="130" t="s">
-        <v>262</v>
-      </c>
-      <c r="D18" s="135">
-        <v>2</v>
-      </c>
-      <c r="E18" s="130" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="33.75" customHeight="1">
-      <c r="A19" s="136" t="s">
-        <v>246</v>
-      </c>
-      <c r="B19" s="131" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="132" t="s">
-        <v>247</v>
-      </c>
-      <c r="D19" s="136">
-        <v>3</v>
-      </c>
-      <c r="E19" s="132" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="33.75" customHeight="1">
-      <c r="A20" s="135"/>
-      <c r="B20" s="129" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="130" t="s">
-        <v>263</v>
-      </c>
-      <c r="D20" s="135">
-        <v>4</v>
-      </c>
-      <c r="E20" s="130" t="s">
-        <v>252</v>
+      <c r="E20" s="104" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="137" t="s">
-        <v>227</v>
-      </c>
-      <c r="B21" s="133"/>
-      <c r="C21" s="134"/>
-      <c r="D21" s="138">
+      <c r="A21" s="111" t="s">
+        <v>226</v>
+      </c>
+      <c r="B21" s="107"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="112">
         <f>SUM(D12:D20)</f>
         <v>32</v>
       </c>
-      <c r="E21" s="134" t="s">
-        <v>251</v>
+      <c r="E21" s="108" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A22" s="161" t="s">
-        <v>265</v>
-      </c>
-      <c r="B22" s="153"/>
-      <c r="C22" s="153"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="153"/>
+      <c r="A22" s="128" t="s">
+        <v>264</v>
+      </c>
+      <c r="B22" s="129"/>
+      <c r="C22" s="129"/>
+      <c r="D22" s="129"/>
+      <c r="E22" s="129"/>
     </row>
     <row r="23" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="162" t="s">
-        <v>226</v>
-      </c>
-      <c r="B23" s="161" t="s">
+      <c r="A23" s="123" t="s">
         <v>225</v>
       </c>
-      <c r="C23" s="126"/>
-      <c r="D23" s="126"/>
-      <c r="E23" s="126"/>
+      <c r="B23" s="128" t="s">
+        <v>224</v>
+      </c>
+      <c r="C23" s="130"/>
+      <c r="D23" s="130"/>
+      <c r="E23" s="130"/>
     </row>
     <row r="24" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="143" t="s">
+      <c r="A24" s="115" t="s">
+        <v>270</v>
+      </c>
+      <c r="B24" s="126" t="s">
+        <v>269</v>
+      </c>
+      <c r="C24" s="127"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
+    </row>
+    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="115" t="s">
+        <v>266</v>
+      </c>
+      <c r="B25" s="126" t="s">
+        <v>277</v>
+      </c>
+      <c r="C25" s="127"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="127"/>
+    </row>
+    <row r="26" spans="1:5" ht="23.25" customHeight="1">
+      <c r="A26" s="128" t="s">
+        <v>281</v>
+      </c>
+      <c r="B26" s="129"/>
+      <c r="C26" s="129"/>
+      <c r="D26" s="129"/>
+      <c r="E26" s="129"/>
+    </row>
+    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="140" t="s">
+        <v>282</v>
+      </c>
+      <c r="B27" s="141"/>
+      <c r="C27" s="141"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="141"/>
+    </row>
+    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A28" s="137" t="s">
+        <v>275</v>
+      </c>
+      <c r="B28" s="139"/>
+      <c r="C28" s="139"/>
+      <c r="D28" s="139"/>
+      <c r="E28" s="138"/>
+    </row>
+    <row r="29" spans="1:5" ht="21" customHeight="1">
+      <c r="A29" s="131" t="s">
+        <v>283</v>
+      </c>
+      <c r="B29" s="132"/>
+      <c r="C29" s="132"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="133"/>
+    </row>
+    <row r="30" spans="1:5" ht="21" customHeight="1">
+      <c r="A30" s="131" t="s">
+        <v>287</v>
+      </c>
+      <c r="B30" s="132"/>
+      <c r="C30" s="132"/>
+      <c r="D30" s="132"/>
+      <c r="E30" s="133"/>
+    </row>
+    <row r="31" spans="1:5" ht="21" customHeight="1">
+      <c r="A31" s="146" t="s">
+        <v>286</v>
+      </c>
+      <c r="B31" s="147"/>
+      <c r="C31" s="147"/>
+      <c r="D31" s="147"/>
+      <c r="E31" s="147"/>
+    </row>
+    <row r="32" spans="1:5" ht="21" customHeight="1">
+      <c r="A32" s="131" t="s">
+        <v>284</v>
+      </c>
+      <c r="B32" s="132"/>
+      <c r="C32" s="132"/>
+      <c r="D32" s="132"/>
+      <c r="E32" s="133"/>
+    </row>
+    <row r="33" spans="1:5" ht="21" customHeight="1">
+      <c r="A33" s="143" t="s">
+        <v>285</v>
+      </c>
+      <c r="B33" s="144"/>
+      <c r="C33" s="144"/>
+      <c r="D33" s="144"/>
+      <c r="E33" s="144"/>
+    </row>
+    <row r="34" spans="1:5" ht="21.95" customHeight="1">
+      <c r="A34" s="128" t="s">
+        <v>276</v>
+      </c>
+      <c r="B34" s="129"/>
+      <c r="C34" s="129"/>
+      <c r="D34" s="129"/>
+      <c r="E34" s="129"/>
+    </row>
+    <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1">
+      <c r="A35" s="123" t="s">
+        <v>223</v>
+      </c>
+      <c r="B35" s="123" t="s">
+        <v>222</v>
+      </c>
+      <c r="C35" s="123" t="s">
         <v>273</v>
       </c>
-      <c r="B24" s="141" t="s">
-        <v>272</v>
-      </c>
-      <c r="C24" s="142"/>
-      <c r="D24" s="142"/>
-      <c r="E24" s="142"/>
-    </row>
-    <row r="25" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="143" t="s">
-        <v>267</v>
-      </c>
-      <c r="B25" s="141" t="s">
-        <v>280</v>
-      </c>
-      <c r="C25" s="142"/>
-      <c r="D25" s="142"/>
-      <c r="E25" s="142"/>
-    </row>
-    <row r="26" spans="1:5" ht="23.25" customHeight="1">
-      <c r="A26" s="161" t="s">
-        <v>284</v>
-      </c>
-      <c r="B26" s="153"/>
-      <c r="C26" s="153"/>
-      <c r="D26" s="153"/>
-      <c r="E26" s="153"/>
-    </row>
-    <row r="27" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="164" t="s">
-        <v>285</v>
-      </c>
-      <c r="B27" s="165"/>
-      <c r="C27" s="165"/>
-      <c r="D27" s="165"/>
-      <c r="E27" s="165"/>
-    </row>
-    <row r="28" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="158" t="s">
-        <v>278</v>
-      </c>
-      <c r="B28" s="159"/>
-      <c r="C28" s="159"/>
-      <c r="D28" s="159"/>
-      <c r="E28" s="160"/>
-    </row>
-    <row r="29" spans="1:5" ht="21" customHeight="1">
-      <c r="A29" s="154" t="s">
-        <v>286</v>
-      </c>
-      <c r="B29" s="155"/>
-      <c r="C29" s="155"/>
-      <c r="D29" s="155"/>
-      <c r="E29" s="156"/>
-    </row>
-    <row r="30" spans="1:5" ht="21" customHeight="1">
-      <c r="A30" s="154" t="s">
-        <v>290</v>
-      </c>
-      <c r="B30" s="155"/>
-      <c r="C30" s="155"/>
-      <c r="D30" s="155"/>
-      <c r="E30" s="156"/>
-    </row>
-    <row r="31" spans="1:5" ht="21" customHeight="1">
-      <c r="A31" s="166" t="s">
-        <v>289</v>
-      </c>
-      <c r="B31" s="167"/>
-      <c r="C31" s="167"/>
-      <c r="D31" s="167"/>
-      <c r="E31" s="167"/>
-    </row>
-    <row r="32" spans="1:5" ht="21" customHeight="1">
-      <c r="A32" s="154" t="s">
-        <v>287</v>
-      </c>
-      <c r="B32" s="155"/>
-      <c r="C32" s="155"/>
-      <c r="D32" s="155"/>
-      <c r="E32" s="156"/>
-    </row>
-    <row r="33" spans="1:5" ht="21" customHeight="1">
-      <c r="A33" s="157" t="s">
-        <v>288</v>
-      </c>
-      <c r="B33" s="163"/>
-      <c r="C33" s="163"/>
-      <c r="D33" s="163"/>
-      <c r="E33" s="163"/>
-    </row>
-    <row r="34" spans="1:5" ht="21.95" customHeight="1">
-      <c r="A34" s="161" t="s">
-        <v>279</v>
-      </c>
-      <c r="B34" s="153"/>
-      <c r="C34" s="153"/>
-      <c r="D34" s="153"/>
-      <c r="E34" s="153"/>
-    </row>
-    <row r="35" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="162" t="s">
-        <v>224</v>
-      </c>
-      <c r="B35" s="162" t="s">
-        <v>223</v>
-      </c>
-      <c r="C35" s="162" t="s">
-        <v>276</v>
-      </c>
-      <c r="D35" s="158" t="s">
-        <v>222</v>
-      </c>
-      <c r="E35" s="160"/>
+      <c r="D35" s="137" t="s">
+        <v>221</v>
+      </c>
+      <c r="E35" s="138"/>
     </row>
     <row r="36" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="139" t="s">
-        <v>221</v>
-      </c>
-      <c r="B36" s="140">
+      <c r="A36" s="113" t="s">
+        <v>220</v>
+      </c>
+      <c r="B36" s="114">
         <v>32</v>
       </c>
-      <c r="C36" s="150">
+      <c r="C36" s="122">
         <f>B36/$B$36</f>
         <v>1</v>
       </c>
-      <c r="D36" s="141"/>
-      <c r="E36" s="142"/>
+      <c r="D36" s="126"/>
+      <c r="E36" s="127"/>
     </row>
     <row r="37" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="139" t="s">
+      <c r="A37" s="113" t="s">
         <v>61</v>
       </c>
-      <c r="B37" s="140">
+      <c r="B37" s="114">
         <v>23</v>
       </c>
-      <c r="C37" s="150">
+      <c r="C37" s="122">
         <f t="shared" ref="C37:C41" si="0">B37/$B$36</f>
         <v>0.71875</v>
       </c>
-      <c r="D37" s="141"/>
-      <c r="E37" s="142"/>
+      <c r="D37" s="126"/>
+      <c r="E37" s="127"/>
     </row>
     <row r="38" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="139" t="s">
+      <c r="A38" s="113" t="s">
         <v>59</v>
       </c>
-      <c r="B38" s="140">
+      <c r="B38" s="114">
         <v>9</v>
       </c>
-      <c r="C38" s="150">
+      <c r="C38" s="122">
         <f t="shared" si="0"/>
         <v>0.28125</v>
       </c>
-      <c r="D38" s="141" t="s">
-        <v>275</v>
-      </c>
-      <c r="E38" s="142"/>
+      <c r="D38" s="126" t="s">
+        <v>272</v>
+      </c>
+      <c r="E38" s="127"/>
     </row>
     <row r="39" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="139" t="s">
-        <v>277</v>
-      </c>
-      <c r="B39" s="140">
+      <c r="A39" s="113" t="s">
+        <v>274</v>
+      </c>
+      <c r="B39" s="114">
         <v>5</v>
       </c>
-      <c r="C39" s="150">
+      <c r="C39" s="122">
         <f>B39/$B$36</f>
         <v>0.15625</v>
       </c>
-      <c r="D39" s="151"/>
-      <c r="E39" s="152"/>
+      <c r="D39" s="135"/>
+      <c r="E39" s="136"/>
     </row>
     <row r="40" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="139" t="s">
+      <c r="A40" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="B40" s="140">
+      <c r="B40" s="114">
         <v>2</v>
       </c>
-      <c r="C40" s="150">
+      <c r="C40" s="122">
         <f t="shared" si="0"/>
         <v>6.25E-2</v>
       </c>
-      <c r="D40" s="151"/>
-      <c r="E40" s="152"/>
+      <c r="D40" s="135"/>
+      <c r="E40" s="136"/>
     </row>
     <row r="41" spans="1:5" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="139" t="s">
-        <v>274</v>
-      </c>
-      <c r="B41" s="140">
+      <c r="A41" s="113" t="s">
+        <v>271</v>
+      </c>
+      <c r="B41" s="114">
         <v>2</v>
       </c>
-      <c r="C41" s="150">
+      <c r="C41" s="122">
         <f t="shared" si="0"/>
         <v>6.25E-2</v>
       </c>
-      <c r="D41" s="141"/>
-      <c r="E41" s="142"/>
+      <c r="D41" s="126"/>
+      <c r="E41" s="127"/>
     </row>
     <row r="42" spans="1:5" ht="20.100000000000001" customHeight="1"/>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="B9:E9"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="D38:E38"/>
@@ -4082,24 +4094,12 @@
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A31:E31"/>
     <mergeCell ref="D37:E37"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="A29:E29"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A34:E34"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4126,53 +4126,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="107" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
+      <c r="A1" s="151" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
       <c r="K1" s="21"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="171" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
+      <c r="A2" s="153" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="153"/>
+      <c r="C2" s="153"/>
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
+      <c r="I2" s="153"/>
+      <c r="J2" s="153"/>
       <c r="K2" s="21"/>
     </row>
-    <row r="3" spans="1:12" s="169" customFormat="1" ht="24" customHeight="1">
-      <c r="A3" s="168" t="s">
-        <v>292</v>
-      </c>
-      <c r="B3" s="168"/>
-      <c r="C3" s="168"/>
-      <c r="D3" s="168"/>
-      <c r="E3" s="168"/>
-      <c r="F3" s="168"/>
-      <c r="G3" s="168"/>
-      <c r="H3" s="168"/>
-      <c r="I3" s="168"/>
-      <c r="J3" s="168"/>
-      <c r="L3" s="170"/>
+    <row r="3" spans="1:12" s="124" customFormat="1" ht="24" customHeight="1">
+      <c r="A3" s="154" t="s">
+        <v>289</v>
+      </c>
+      <c r="B3" s="154"/>
+      <c r="C3" s="154"/>
+      <c r="D3" s="154"/>
+      <c r="E3" s="154"/>
+      <c r="F3" s="154"/>
+      <c r="G3" s="154"/>
+      <c r="H3" s="154"/>
+      <c r="I3" s="154"/>
+      <c r="J3" s="154"/>
+      <c r="L3" s="125"/>
     </row>
     <row r="4" spans="1:12" ht="25.5" customHeight="1">
       <c r="A4" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>68</v>
@@ -4208,22 +4208,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C5" s="55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E5" s="65" t="s">
         <v>74</v>
       </c>
       <c r="F5" s="85" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G5" s="65" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H5" s="64" t="s">
         <v>59</v>
@@ -4232,7 +4232,7 @@
         <v>15</v>
       </c>
       <c r="J5" s="65" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L5" s="21"/>
     </row>
@@ -4241,22 +4241,22 @@
         <v>9</v>
       </c>
       <c r="B6" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C6" s="54" t="s">
         <v>18</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E6" s="66" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F6" s="89" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G6" s="67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H6" s="56" t="s">
         <v>59</v>
@@ -4265,7 +4265,7 @@
         <v>13</v>
       </c>
       <c r="J6" s="67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L6" s="21"/>
     </row>
@@ -4273,20 +4273,20 @@
       <c r="A7" s="30">
         <v>16</v>
       </c>
-      <c r="B7" s="110" t="s">
+      <c r="B7" s="155" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="158" t="s">
         <v>112</v>
-      </c>
-      <c r="C7" s="110" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="113" t="s">
-        <v>113</v>
       </c>
       <c r="E7" s="65" t="s">
         <v>60</v>
       </c>
       <c r="F7" s="85" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G7" s="65" t="s">
         <v>83</v>
@@ -4306,14 +4306,14 @@
       <c r="A8" s="30">
         <v>17</v>
       </c>
-      <c r="B8" s="111"/>
-      <c r="C8" s="111"/>
-      <c r="D8" s="114"/>
+      <c r="B8" s="156"/>
+      <c r="C8" s="156"/>
+      <c r="D8" s="159"/>
       <c r="E8" s="67" t="s">
         <v>60</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G8" s="67" t="s">
         <v>82</v>
@@ -4322,7 +4322,7 @@
         <v>59</v>
       </c>
       <c r="I8" s="52" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J8" s="67" t="s">
         <v>80</v>
@@ -4333,8 +4333,8 @@
       <c r="A9" s="30">
         <v>20</v>
       </c>
-      <c r="B9" s="111"/>
-      <c r="C9" s="112"/>
+      <c r="B9" s="156"/>
+      <c r="C9" s="157"/>
       <c r="D9" s="53" t="s">
         <v>73</v>
       </c>
@@ -4342,10 +4342,10 @@
         <v>74</v>
       </c>
       <c r="F9" s="85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G9" s="65" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H9" s="64" t="s">
         <v>59</v>
@@ -4354,7 +4354,7 @@
         <v>62</v>
       </c>
       <c r="J9" s="65" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L9" s="21"/>
     </row>
@@ -4362,21 +4362,21 @@
       <c r="A10" s="30">
         <v>25</v>
       </c>
-      <c r="B10" s="112"/>
+      <c r="B10" s="157"/>
       <c r="C10" s="54" t="s">
         <v>21</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E10" s="67" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F10" s="89" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G10" s="67" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H10" s="56" t="s">
         <v>59</v>
@@ -4385,7 +4385,7 @@
         <v>14</v>
       </c>
       <c r="J10" s="67" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L10" s="21"/>
     </row>
@@ -4393,23 +4393,23 @@
       <c r="A11" s="30">
         <v>26</v>
       </c>
-      <c r="B11" s="104" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="104" t="s">
+      <c r="B11" s="148" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" s="148" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E11" s="69" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" s="86" t="s">
+        <v>204</v>
+      </c>
+      <c r="G11" s="69" t="s">
         <v>144</v>
-      </c>
-      <c r="F11" s="86" t="s">
-        <v>205</v>
-      </c>
-      <c r="G11" s="69" t="s">
-        <v>145</v>
       </c>
       <c r="H11" s="68" t="s">
         <v>59</v>
@@ -4418,26 +4418,26 @@
         <v>7</v>
       </c>
       <c r="J11" s="69" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="73.5" customHeight="1">
       <c r="A12" s="30">
         <v>28</v>
       </c>
-      <c r="B12" s="105"/>
-      <c r="C12" s="106"/>
+      <c r="B12" s="149"/>
+      <c r="C12" s="150"/>
       <c r="D12" s="53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E12" s="70" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F12" s="88" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G12" s="70" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H12" s="57" t="s">
         <v>59</v>
@@ -4446,28 +4446,28 @@
         <v>11</v>
       </c>
       <c r="J12" s="70" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="73.5" customHeight="1">
       <c r="A13" s="30">
         <v>31</v>
       </c>
-      <c r="B13" s="106"/>
+      <c r="B13" s="150"/>
       <c r="C13" s="55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D13" s="53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E13" s="65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F13" s="85" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G13" s="65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H13" s="64" t="s">
         <v>59</v>
@@ -4476,7 +4476,7 @@
         <v>12</v>
       </c>
       <c r="J13" s="65" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="48" customHeight="1">
@@ -4503,6 +4503,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4526,82 +4527,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="36" customHeight="1">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="162" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
+      <c r="B1" s="163"/>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
+      <c r="G1" s="163"/>
+      <c r="H1" s="163"/>
+      <c r="I1" s="163"/>
+      <c r="J1" s="163"/>
+      <c r="K1" s="163"/>
     </row>
     <row r="2" spans="1:12" ht="24" customHeight="1">
-      <c r="A2" s="115" t="s">
-        <v>283</v>
-      </c>
-      <c r="B2" s="116"/>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
+      <c r="A2" s="160" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="161"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
     </row>
     <row r="3" spans="1:12" s="82" customFormat="1" ht="24" customHeight="1">
-      <c r="A3" s="118" t="s">
-        <v>282</v>
-      </c>
-      <c r="B3" s="118"/>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="118"/>
-      <c r="K3" s="118"/>
-    </row>
-    <row r="4" spans="1:12" s="145" customFormat="1" ht="24" customHeight="1">
-      <c r="A4" s="146" t="s">
+      <c r="A3" s="164" t="s">
+        <v>279</v>
+      </c>
+      <c r="B3" s="164"/>
+      <c r="C3" s="164"/>
+      <c r="D3" s="164"/>
+      <c r="E3" s="164"/>
+      <c r="F3" s="164"/>
+      <c r="G3" s="164"/>
+      <c r="H3" s="164"/>
+      <c r="I3" s="164"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="164"/>
+    </row>
+    <row r="4" spans="1:12" s="117" customFormat="1" ht="24" customHeight="1">
+      <c r="A4" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="146" t="s">
+      <c r="B4" s="118" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="147" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="146" t="s">
+      <c r="C4" s="119" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="146" t="s">
+      <c r="E4" s="118" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="147" t="s">
+      <c r="F4" s="119" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="146" t="s">
+      <c r="G4" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="146" t="s">
+      <c r="H4" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="146" t="s">
+      <c r="I4" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="147" t="s">
+      <c r="J4" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="148" t="s">
+      <c r="K4" s="120" t="s">
         <v>25</v>
       </c>
     </row>
@@ -4616,13 +4617,13 @@
         <v>32</v>
       </c>
       <c r="D5" s="77" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E5" s="71" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>46</v>
@@ -4649,7 +4650,7 @@
         <v>31</v>
       </c>
       <c r="D6" s="78" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E6" s="72" t="s">
         <v>17</v>
@@ -4664,7 +4665,7 @@
         <v>24</v>
       </c>
       <c r="I6" s="78" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>37</v>
@@ -4679,10 +4680,10 @@
         <v>46104</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D7" s="77" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E7" s="71" t="s">
         <v>18</v>
@@ -4700,7 +4701,7 @@
         <v>20</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K7" s="7"/>
     </row>
@@ -4715,16 +4716,16 @@
         <v>41</v>
       </c>
       <c r="D8" s="78" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E8" s="72" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>89</v>
+        <v>294</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>88</v>
@@ -4748,13 +4749,13 @@
         <v>19</v>
       </c>
       <c r="D9" s="77" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E9" s="71" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>57</v>
@@ -4766,7 +4767,7 @@
         <v>38</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>58</v>
@@ -4783,7 +4784,7 @@
         <v>42</v>
       </c>
       <c r="D10" s="79" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E10" s="72" t="s">
         <v>22</v>
@@ -4816,7 +4817,7 @@
         <v>36</v>
       </c>
       <c r="D11" s="77" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E11" s="71" t="s">
         <v>18</v>
@@ -4831,7 +4832,7 @@
         <v>54</v>
       </c>
       <c r="I11" s="77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>51</v>
@@ -4840,7 +4841,7 @@
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="116.25" customHeight="1">
       <c r="A12" s="72" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B12" s="75">
         <v>46121</v>
@@ -4849,7 +4850,7 @@
         <v>52</v>
       </c>
       <c r="D12" s="78" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E12" s="72" t="s">
         <v>22</v>
@@ -4861,13 +4862,13 @@
         <v>55</v>
       </c>
       <c r="H12" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I12" s="78" t="s">
+        <v>174</v>
+      </c>
+      <c r="J12" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="I12" s="78" t="s">
-        <v>175</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="K12" s="18"/>
     </row>
@@ -4882,7 +4883,7 @@
         <v>29</v>
       </c>
       <c r="D13" s="80" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E13" s="81" t="s">
         <v>21</v>
@@ -5020,38 +5021,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33.950000000000003" customHeight="1">
-      <c r="A1" s="108" t="s">
-        <v>97</v>
-      </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
-      <c r="H1" s="108"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
+      <c r="A1" s="152" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="152"/>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="152"/>
+      <c r="G1" s="152"/>
+      <c r="H1" s="152"/>
+      <c r="I1" s="152"/>
+      <c r="J1" s="152"/>
       <c r="K1" s="20"/>
     </row>
     <row r="2" spans="1:12" ht="23.25" customHeight="1">
-      <c r="A2" s="109" t="s">
-        <v>291</v>
-      </c>
-      <c r="B2" s="109"/>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
-      <c r="F2" s="109"/>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
+      <c r="A2" s="168" t="s">
+        <v>288</v>
+      </c>
+      <c r="B2" s="168"/>
+      <c r="C2" s="168"/>
+      <c r="D2" s="168"/>
+      <c r="E2" s="168"/>
+      <c r="F2" s="168"/>
+      <c r="G2" s="168"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="168"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" spans="1:12" s="145" customFormat="1" ht="27.95" customHeight="1">
+    <row r="3" spans="1:12" s="117" customFormat="1" ht="27.95" customHeight="1">
       <c r="A3" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>68</v>
@@ -5080,29 +5081,29 @@
       <c r="J3" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="K3" s="144"/>
+      <c r="K3" s="116"/>
     </row>
     <row r="4" spans="1:12" ht="70.5" customHeight="1">
       <c r="A4" s="30">
         <v>1</v>
       </c>
-      <c r="B4" s="104" t="s">
+      <c r="B4" s="148" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="54" t="s">
-        <v>118</v>
-      </c>
       <c r="D4" s="52" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E4" s="92" t="s">
         <v>74</v>
       </c>
       <c r="F4" s="84" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H4" s="29" t="s">
         <v>61</v>
@@ -5115,21 +5116,21 @@
       <c r="A5" s="30">
         <v>2</v>
       </c>
-      <c r="B5" s="105"/>
-      <c r="C5" s="110" t="s">
-        <v>119</v>
+      <c r="B5" s="149"/>
+      <c r="C5" s="155" t="s">
+        <v>118</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E5" s="93" t="s">
         <v>74</v>
       </c>
       <c r="F5" s="85" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>61</v>
@@ -5142,19 +5143,19 @@
       <c r="A6" s="30">
         <v>3</v>
       </c>
-      <c r="B6" s="105"/>
-      <c r="C6" s="112"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="157"/>
       <c r="D6" s="52" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E6" s="92" t="s">
         <v>74</v>
       </c>
       <c r="F6" s="84" t="s">
+        <v>217</v>
+      </c>
+      <c r="G6" s="26" t="s">
         <v>218</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>219</v>
       </c>
       <c r="H6" s="29" t="s">
         <v>61</v>
@@ -5167,21 +5168,21 @@
       <c r="A7" s="30">
         <v>4</v>
       </c>
-      <c r="B7" s="105"/>
+      <c r="B7" s="149"/>
       <c r="C7" s="55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7" s="53" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E7" s="94" t="s">
         <v>74</v>
       </c>
       <c r="F7" s="85" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>59</v>
@@ -5190,7 +5191,7 @@
         <v>15</v>
       </c>
       <c r="J7" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L7" s="23"/>
     </row>
@@ -5198,21 +5199,21 @@
       <c r="A8" s="30">
         <v>5</v>
       </c>
-      <c r="B8" s="105"/>
-      <c r="C8" s="104" t="s">
+      <c r="B8" s="149"/>
+      <c r="C8" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="119" t="s">
-        <v>126</v>
+      <c r="D8" s="165" t="s">
+        <v>125</v>
       </c>
       <c r="E8" s="92" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F8" s="84" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H8" s="29" t="s">
         <v>61</v>
@@ -5225,17 +5226,17 @@
       <c r="A9" s="30">
         <v>6</v>
       </c>
-      <c r="B9" s="105"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="120"/>
+      <c r="B9" s="149"/>
+      <c r="C9" s="149"/>
+      <c r="D9" s="167"/>
       <c r="E9" s="102" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F9" s="85" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H9" s="27" t="s">
         <v>61</v>
@@ -5248,19 +5249,19 @@
       <c r="A10" s="30">
         <v>7</v>
       </c>
-      <c r="B10" s="105"/>
-      <c r="C10" s="105"/>
-      <c r="D10" s="119" t="s">
-        <v>120</v>
+      <c r="B10" s="149"/>
+      <c r="C10" s="149"/>
+      <c r="D10" s="165" t="s">
+        <v>119</v>
       </c>
       <c r="E10" s="92" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F10" s="84" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H10" s="29" t="s">
         <v>61</v>
@@ -5273,17 +5274,17 @@
       <c r="A11" s="30">
         <v>8</v>
       </c>
-      <c r="B11" s="106"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="120"/>
+      <c r="B11" s="150"/>
+      <c r="C11" s="150"/>
+      <c r="D11" s="167"/>
       <c r="E11" s="94" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F11" s="85" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H11" s="27" t="s">
         <v>61</v>
@@ -5296,23 +5297,23 @@
       <c r="A12" s="30">
         <v>9</v>
       </c>
-      <c r="B12" s="104" t="s">
+      <c r="B12" s="148" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="148" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="C12" s="104" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="52" t="s">
-        <v>96</v>
-      </c>
       <c r="E12" s="95" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F12" s="84" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G12" s="26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H12" s="29" t="s">
         <v>59</v>
@@ -5321,7 +5322,7 @@
         <v>13</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L12" s="20"/>
     </row>
@@ -5329,19 +5330,19 @@
       <c r="A13" s="30">
         <v>10</v>
       </c>
-      <c r="B13" s="105"/>
-      <c r="C13" s="106"/>
+      <c r="B13" s="149"/>
+      <c r="C13" s="150"/>
       <c r="D13" s="53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E13" s="96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F13" s="85" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H13" s="27" t="s">
         <v>61</v>
@@ -5354,21 +5355,21 @@
       <c r="A14" s="30">
         <v>11</v>
       </c>
-      <c r="B14" s="105"/>
-      <c r="C14" s="104" t="s">
+      <c r="B14" s="149"/>
+      <c r="C14" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="119" t="s">
-        <v>106</v>
+      <c r="D14" s="165" t="s">
+        <v>105</v>
       </c>
       <c r="E14" s="95" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F14" s="84" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G14" s="26" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H14" s="29" t="s">
         <v>61</v>
@@ -5381,17 +5382,17 @@
       <c r="A15" s="30">
         <v>12</v>
       </c>
-      <c r="B15" s="105"/>
-      <c r="C15" s="105"/>
-      <c r="D15" s="120"/>
+      <c r="B15" s="149"/>
+      <c r="C15" s="149"/>
+      <c r="D15" s="167"/>
       <c r="E15" s="97" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F15" s="85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H15" s="27" t="s">
         <v>61</v>
@@ -5404,19 +5405,19 @@
       <c r="A16" s="30">
         <v>13</v>
       </c>
-      <c r="B16" s="105"/>
-      <c r="C16" s="105"/>
+      <c r="B16" s="149"/>
+      <c r="C16" s="149"/>
       <c r="D16" s="52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E16" s="95" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F16" s="84" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G16" s="26" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H16" s="29" t="s">
         <v>61</v>
@@ -5429,19 +5430,19 @@
       <c r="A17" s="30">
         <v>14</v>
       </c>
-      <c r="B17" s="106"/>
-      <c r="C17" s="106"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="150"/>
       <c r="D17" s="53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E17" s="96" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F17" s="85" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H17" s="27" t="s">
         <v>61</v>
@@ -5453,20 +5454,20 @@
       <c r="A18" s="30">
         <v>15</v>
       </c>
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="122" t="s">
+      <c r="C18" s="169" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="119" t="s">
+      <c r="D18" s="165" t="s">
         <v>72</v>
       </c>
       <c r="E18" s="92" t="s">
         <v>74</v>
       </c>
       <c r="F18" s="84" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>75</v>
@@ -5481,14 +5482,14 @@
       <c r="A19" s="30">
         <v>16</v>
       </c>
-      <c r="B19" s="105"/>
-      <c r="C19" s="123"/>
-      <c r="D19" s="121"/>
+      <c r="B19" s="149"/>
+      <c r="C19" s="170"/>
+      <c r="D19" s="166"/>
       <c r="E19" s="93" t="s">
         <v>60</v>
       </c>
       <c r="F19" s="85" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G19" s="28" t="s">
         <v>83</v>
@@ -5507,23 +5508,23 @@
       <c r="A20" s="30">
         <v>17</v>
       </c>
-      <c r="B20" s="105"/>
-      <c r="C20" s="123"/>
-      <c r="D20" s="121"/>
+      <c r="B20" s="149"/>
+      <c r="C20" s="170"/>
+      <c r="D20" s="166"/>
       <c r="E20" s="92" t="s">
         <v>60</v>
       </c>
       <c r="F20" s="84" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G20" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H20" s="29" t="s">
         <v>59</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J20" s="26" t="s">
         <v>80</v>
@@ -5533,14 +5534,14 @@
       <c r="A21" s="30">
         <v>18</v>
       </c>
-      <c r="B21" s="105"/>
-      <c r="C21" s="123"/>
-      <c r="D21" s="120"/>
+      <c r="B21" s="149"/>
+      <c r="C21" s="170"/>
+      <c r="D21" s="167"/>
       <c r="E21" s="102" t="s">
         <v>60</v>
       </c>
       <c r="F21" s="85" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G21" s="28" t="s">
         <v>86</v>
@@ -5555,16 +5556,16 @@
       <c r="A22" s="30">
         <v>19</v>
       </c>
-      <c r="B22" s="105"/>
-      <c r="C22" s="123"/>
-      <c r="D22" s="119" t="s">
+      <c r="B22" s="149"/>
+      <c r="C22" s="170"/>
+      <c r="D22" s="165" t="s">
         <v>73</v>
       </c>
       <c r="E22" s="92" t="s">
         <v>74</v>
       </c>
       <c r="F22" s="84" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>85</v>
@@ -5579,17 +5580,17 @@
       <c r="A23" s="30">
         <v>20</v>
       </c>
-      <c r="B23" s="105"/>
-      <c r="C23" s="123"/>
-      <c r="D23" s="121"/>
+      <c r="B23" s="149"/>
+      <c r="C23" s="170"/>
+      <c r="D23" s="166"/>
       <c r="E23" s="93" t="s">
         <v>60</v>
       </c>
       <c r="F23" s="85" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H23" s="27" t="s">
         <v>59</v>
@@ -5598,24 +5599,24 @@
         <v>62</v>
       </c>
       <c r="J23" s="32" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="70.5" customHeight="1">
       <c r="A24" s="30">
         <v>21</v>
       </c>
-      <c r="B24" s="105"/>
-      <c r="C24" s="123"/>
-      <c r="D24" s="120"/>
+      <c r="B24" s="149"/>
+      <c r="C24" s="170"/>
+      <c r="D24" s="167"/>
       <c r="E24" s="92" t="s">
         <v>60</v>
       </c>
       <c r="F24" s="84" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G24" s="26" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H24" s="29" t="s">
         <v>61</v>
@@ -5627,19 +5628,19 @@
       <c r="A25" s="30">
         <v>22</v>
       </c>
-      <c r="B25" s="105"/>
-      <c r="C25" s="123"/>
-      <c r="D25" s="113" t="s">
+      <c r="B25" s="149"/>
+      <c r="C25" s="170"/>
+      <c r="D25" s="158" t="s">
         <v>84</v>
       </c>
       <c r="E25" s="93" t="s">
         <v>74</v>
       </c>
       <c r="F25" s="85" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H25" s="27" t="s">
         <v>61</v>
@@ -5651,17 +5652,17 @@
       <c r="A26" s="30">
         <v>23</v>
       </c>
-      <c r="B26" s="105"/>
-      <c r="C26" s="124"/>
-      <c r="D26" s="114"/>
+      <c r="B26" s="149"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="159"/>
       <c r="E26" s="92" t="s">
         <v>60</v>
       </c>
       <c r="F26" s="84" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G26" s="26" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H26" s="29" t="s">
         <v>61</v>
@@ -5673,21 +5674,21 @@
       <c r="A27" s="30">
         <v>24</v>
       </c>
-      <c r="B27" s="105"/>
-      <c r="C27" s="110" t="s">
+      <c r="B27" s="149"/>
+      <c r="C27" s="155" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="113" t="s">
-        <v>115</v>
+      <c r="D27" s="158" t="s">
+        <v>114</v>
       </c>
       <c r="E27" s="94" t="s">
         <v>74</v>
       </c>
       <c r="F27" s="85" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G27" s="28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H27" s="27" t="s">
         <v>61</v>
@@ -5699,17 +5700,17 @@
       <c r="A28" s="30">
         <v>25</v>
       </c>
-      <c r="B28" s="106"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="114"/>
+      <c r="B28" s="150"/>
+      <c r="C28" s="157"/>
+      <c r="D28" s="159"/>
       <c r="E28" s="92" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F28" s="84" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G28" s="26" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H28" s="29" t="s">
         <v>59</v>
@@ -5718,30 +5719,30 @@
         <v>14</v>
       </c>
       <c r="J28" s="26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="22" customFormat="1" ht="70.5" customHeight="1">
       <c r="A29" s="30">
         <v>26</v>
       </c>
-      <c r="B29" s="104" t="s">
-        <v>134</v>
-      </c>
-      <c r="C29" s="104" t="s">
+      <c r="B29" s="148" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="148" t="s">
         <v>18</v>
       </c>
       <c r="D29" s="53" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E29" s="98" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F29" s="86" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G29" s="101" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H29" s="37" t="s">
         <v>59</v>
@@ -5750,26 +5751,26 @@
         <v>7</v>
       </c>
       <c r="J29" s="33" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="70.5" customHeight="1">
       <c r="A30" s="30">
         <v>27</v>
       </c>
-      <c r="B30" s="105"/>
-      <c r="C30" s="105"/>
+      <c r="B30" s="149"/>
+      <c r="C30" s="149"/>
       <c r="D30" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E30" s="92" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F30" s="84" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G30" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H30" s="29" t="s">
         <v>61</v>
@@ -5781,19 +5782,19 @@
       <c r="A31" s="30">
         <v>28</v>
       </c>
-      <c r="B31" s="105"/>
-      <c r="C31" s="106"/>
+      <c r="B31" s="149"/>
+      <c r="C31" s="150"/>
       <c r="D31" s="53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E31" s="99" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F31" s="85" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G31" s="91" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H31" s="27" t="s">
         <v>59</v>
@@ -5802,28 +5803,28 @@
         <v>11</v>
       </c>
       <c r="J31" s="32" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="70.5" customHeight="1">
       <c r="A32" s="30">
         <v>29</v>
       </c>
-      <c r="B32" s="105"/>
-      <c r="C32" s="104" t="s">
-        <v>149</v>
-      </c>
-      <c r="D32" s="119" t="s">
-        <v>151</v>
+      <c r="B32" s="149"/>
+      <c r="C32" s="148" t="s">
+        <v>148</v>
+      </c>
+      <c r="D32" s="165" t="s">
+        <v>150</v>
       </c>
       <c r="E32" s="100" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F32" s="87" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G32" s="31" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H32" s="35" t="s">
         <v>61</v>
@@ -5835,17 +5836,17 @@
       <c r="A33" s="30">
         <v>30</v>
       </c>
-      <c r="B33" s="105"/>
-      <c r="C33" s="105"/>
-      <c r="D33" s="121"/>
+      <c r="B33" s="149"/>
+      <c r="C33" s="149"/>
+      <c r="D33" s="166"/>
       <c r="E33" s="99" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F33" s="85" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G33" s="32" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H33" s="27" t="s">
         <v>61</v>
@@ -5857,17 +5858,17 @@
       <c r="A34" s="30">
         <v>31</v>
       </c>
-      <c r="B34" s="105"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="121"/>
+      <c r="B34" s="149"/>
+      <c r="C34" s="149"/>
+      <c r="D34" s="166"/>
       <c r="E34" s="100" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F34" s="87" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G34" s="31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H34" s="35" t="s">
         <v>59</v>
@@ -5876,24 +5877,24 @@
         <v>12</v>
       </c>
       <c r="J34" s="31" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="22" customFormat="1" ht="70.5" customHeight="1">
       <c r="A35" s="30">
         <v>32</v>
       </c>
-      <c r="B35" s="106"/>
-      <c r="C35" s="106"/>
-      <c r="D35" s="120"/>
+      <c r="B35" s="150"/>
+      <c r="C35" s="150"/>
+      <c r="D35" s="167"/>
       <c r="E35" s="99" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F35" s="85" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G35" s="32" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H35" s="27" t="s">
         <v>61</v>
@@ -6110,6 +6111,12 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B4:B11"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="D10:D11"/>
     <mergeCell ref="B29:B35"/>
     <mergeCell ref="C29:C31"/>
     <mergeCell ref="C32:C35"/>
@@ -6126,12 +6133,6 @@
     <mergeCell ref="B18:B28"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="D27:D28"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B4:B11"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="D10:D11"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <dataValidations count="1">
